--- a/vse-loti/339915166/spec-339915166.xlsx
+++ b/vse-loti/339915166/spec-339915166.xlsx
@@ -16,7 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="#,##0.00&quot; ₽&quot;"/>
+  </numFmts>
   <fonts count="3">
     <font>
       <name val="Calibri"/>
@@ -58,12 +60,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H5"/>
+  <dimension ref="A1:I7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -450,51 +454,110 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Наименование позиции (⌀ + s, если указано)</t>
+          <t>Наименование позиции</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>D×s, мм</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
           <t>Кол-во (исх.)</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Ед. изм.</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Масса, т (приведённая)</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Стоимость (без НДС)</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Цена за т (без НДС)</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Цена за т (с НДС)</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>ости участникам в зонах проведения мероприятия. Вода питьевая из расчета не менее</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>литр</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>диаметр от</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>м</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr"/>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
         <is>
           <t>ИТОГО</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Источник: Приложение  к Разделу 6 Документации -   Расчет НМЦ.xlsx</t>
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>НМЦК из обоснования:</t>
+        </is>
+      </c>
+      <c r="G5" s="4" t="n">
+        <v>160000000</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Источник: Приложение №1 к Документации - Техническое задание.txt</t>
         </is>
       </c>
     </row>
